--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -2055,12 +2055,72 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>2.98982</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="B68" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -3095,12 +3155,72 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>2.99242</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="B68" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -3882,10 +4002,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.3365</v>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>-50.7133%</t>
         </is>
@@ -3902,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4668,12 +4848,72 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1.00105</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-51.2238%</t>
+      <c r="B51" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-66.5965%</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -5450,10 +5690,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.3365</v>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>-50.7133%</t>
         </is>
@@ -5470,7 +5770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -6236,12 +6536,72 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1.00105</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-51.2238%</t>
+      <c r="B51" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-66.5965%</t>
         </is>
       </c>
     </row>

--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -2115,10 +2115,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="0" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>-0.343%</t>
         </is>
@@ -2136,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -3215,10 +3275,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="0" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
@@ -3236,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4062,10 +4182,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>0.50474</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>-50.7133%</t>
         </is>
@@ -4082,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4908,10 +5088,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>1.50158</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>-66.5965%</t>
         </is>
@@ -4929,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -5750,10 +5990,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>0.50474</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>-50.7133%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.50474</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>-50.7133%</t>
         </is>
@@ -5770,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -6596,10 +6896,70 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>1.50158</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.50158</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>-66.5965%</t>
         </is>

--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2055,130 +2055,10 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B69" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>-0.343%</t>
         </is>
@@ -2196,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -2230,7 +2110,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2125,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2155,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2170,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3215,130 +3095,10 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B69" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
@@ -3356,7 +3116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -3392,7 +3152,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3167,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3182,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3197,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3362,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3377,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3557,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3572,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3587,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3602,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3617,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3677,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3692,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3707,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4122,132 +3882,12 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
+      <c r="B51" t="n">
+        <v>1.00949</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-1.4257%</t>
         </is>
       </c>
     </row>
@@ -4262,7 +3902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -4298,7 +3938,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4313,7 +3953,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4328,7 +3968,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4343,7 +3983,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4148,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4163,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4178,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4193,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4343,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4373,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4388,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4403,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4463,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4478,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4493,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5028,132 +4668,12 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-66.5965%</t>
+      <c r="B51" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-2.4486%</t>
         </is>
       </c>
     </row>
@@ -5169,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -5200,7 +4720,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5215,7 +4735,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5230,7 +4750,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5245,7 +4765,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5410,7 +4930,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +4945,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5125,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5140,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5155,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5170,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5185,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5245,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5260,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5275,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5930,132 +5450,12 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.50474</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-50.7133%</t>
+      <c r="B51" t="n">
+        <v>2.01898</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -6070,7 +5470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -6106,7 +5506,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6121,7 +5521,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6136,7 +5536,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6151,7 +5551,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6316,7 +5716,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +5731,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6346,7 +5746,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6361,7 +5761,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6511,7 +5911,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6541,7 +5941,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +5956,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6571,7 +5971,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6031,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6046,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6061,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6836,132 +6236,12 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="B51" t="n">
+        <v>2.0063</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1.50158</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-66.5965%</t>
         </is>
       </c>
     </row>

--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="22095" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -631,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -642,11 +642,42 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -657,7 +688,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1036,1031 +1066,1557 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="7" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="8" min="3" max="3"/>
+    <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
+    <col width="16.375" customWidth="1" style="13" min="2" max="2"/>
+    <col width="15.25" customWidth="1" style="14" min="3" max="3"/>
+    <col width="15.875" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16.125" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9" customWidth="1" style="5" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="15" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="5" t="n">
         <v>0.99998</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>-0.002%</t>
         </is>
       </c>
+      <c r="D4" s="5" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="5" t="n">
         <v>1.00004</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
+      <c r="D6" s="5" t="n">
+        <v>1.00004</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D7" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D8" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="5" t="n">
         <v>0.99956</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D9" s="5" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="5" t="n">
         <v>0.99986</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>-0.018%</t>
         </is>
       </c>
+      <c r="D10" s="5" t="n">
+        <v>0.99986</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-0.018%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="5" t="n">
         <v>0.99958</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>-0.046%</t>
         </is>
       </c>
+      <c r="D11" s="5" t="n">
+        <v>0.99958</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.046%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="5" t="n">
         <v>0.99984</v>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D12" s="5" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="5" t="n">
         <v>0.99984</v>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D13" s="5" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="5" t="n">
         <v>0.9994</v>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>-0.064%</t>
         </is>
       </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-0.064%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="5" t="n">
         <v>0.99938</v>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>-0.066%</t>
         </is>
       </c>
+      <c r="D15" s="5" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-0.066%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="5" t="n">
         <v>0.99905</v>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>-0.099%</t>
         </is>
       </c>
+      <c r="D16" s="5" t="n">
+        <v>0.99905</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-0.099%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="5" t="n">
         <v>0.99771</v>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>-0.233%</t>
         </is>
       </c>
+      <c r="D17" s="5" t="n">
+        <v>0.99771</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-0.233%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="5" t="n">
         <v>0.99775</v>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>-0.229%</t>
         </is>
       </c>
+      <c r="D18" s="5" t="n">
+        <v>0.99775</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-0.229%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="5" t="n">
         <v>0.99776</v>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>-0.228%</t>
         </is>
       </c>
+      <c r="D19" s="5" t="n">
+        <v>0.99776</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>-0.228%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>-0.224%</t>
         </is>
       </c>
+      <c r="D20" s="5" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>-0.224%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="5" t="n">
         <v>0.99788</v>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>-0.216%</t>
         </is>
       </c>
+      <c r="D21" s="5" t="n">
+        <v>0.99788</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-0.216%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="5" t="n">
         <v>0.99798</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>-0.206%</t>
         </is>
       </c>
+      <c r="D22" s="5" t="n">
+        <v>0.99798</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>-0.206%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="5" t="n">
         <v>0.9980599999999999</v>
       </c>
-      <c r="C23" s="0" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>-0.198%</t>
         </is>
       </c>
+      <c r="D23" s="5" t="n">
+        <v>0.9980599999999999</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>-0.198%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="5" t="n">
         <v>0.99799</v>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>-0.205%</t>
         </is>
       </c>
+      <c r="D24" s="5" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>-0.205%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="5" t="n">
         <v>0.9981</v>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>-0.194%</t>
         </is>
       </c>
+      <c r="D25" s="5" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>-0.194%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="5" t="n">
         <v>0.99813</v>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>-0.191%</t>
         </is>
       </c>
+      <c r="D26" s="5" t="n">
+        <v>0.99813</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>-0.191%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="5" t="n">
         <v>0.99825</v>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>-0.179%</t>
         </is>
       </c>
+      <c r="D27" s="5" t="n">
+        <v>0.99825</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>-0.179%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="5" t="n">
         <v>0.99829</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>-0.175%</t>
         </is>
       </c>
+      <c r="D28" s="5" t="n">
+        <v>0.99829</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>-0.175%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="5" t="n">
         <v>0.99873</v>
       </c>
-      <c r="C29" s="0" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>-0.131%</t>
         </is>
       </c>
+      <c r="D29" s="5" t="n">
+        <v>0.99873</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>-0.131%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="5" t="n">
         <v>0.99878</v>
       </c>
-      <c r="C30" s="0" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>-0.126%</t>
         </is>
       </c>
+      <c r="D30" s="5" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>-0.126%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="5" t="n">
         <v>0.99913</v>
       </c>
-      <c r="C31" s="0" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>-0.091%</t>
         </is>
       </c>
+      <c r="D31" s="5" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-0.091%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="5" t="n">
         <v>0.9952299999999999</v>
       </c>
-      <c r="C32" s="0" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>-0.481%</t>
         </is>
       </c>
+      <c r="D32" s="5" t="n">
+        <v>0.9952299999999999</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>-0.481%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="5" t="n">
         <v>0.99587</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D33" s="5" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="5" t="n">
         <v>0.9958900000000001</v>
       </c>
-      <c r="C34" s="0" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>-0.415%</t>
         </is>
       </c>
+      <c r="D34" s="5" t="n">
+        <v>0.9958900000000001</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>-0.415%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="5" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C35" s="0" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>-0.411%</t>
         </is>
       </c>
+      <c r="D35" s="5" t="n">
+        <v>0.99593</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>-0.411%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="5" t="n">
         <v>0.99627</v>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>-0.377%</t>
         </is>
       </c>
+      <c r="D36" s="5" t="n">
+        <v>0.99627</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>-0.377%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="5" t="n">
         <v>0.99875</v>
       </c>
-      <c r="C37" s="0" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>-0.129%</t>
         </is>
       </c>
+      <c r="D37" s="5" t="n">
+        <v>0.99875</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>-0.129%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="5" t="n">
         <v>0.9988</v>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>-0.124%</t>
         </is>
       </c>
+      <c r="D38" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>-0.124%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="5" t="n">
         <v>0.9988899999999999</v>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>-0.115%</t>
         </is>
       </c>
+      <c r="D39" s="5" t="n">
+        <v>0.9988899999999999</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>-0.115%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="5" t="n">
         <v>0.99826</v>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>-0.178%</t>
         </is>
       </c>
+      <c r="D40" s="5" t="n">
+        <v>0.99826</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>-0.178%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="5" t="n">
         <v>0.9972299999999999</v>
       </c>
-      <c r="C41" s="0" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>-0.281%</t>
         </is>
       </c>
+      <c r="D41" s="5" t="n">
+        <v>0.9972299999999999</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>-0.281%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="5" t="n">
         <v>0.99742</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>-0.262%</t>
         </is>
       </c>
+      <c r="D42" s="5" t="n">
+        <v>0.99742</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>-0.262%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="5" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D43" s="5" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="5" t="n">
         <v>0.9978399999999999</v>
       </c>
-      <c r="C44" s="0" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>-0.22%</t>
         </is>
       </c>
+      <c r="D44" s="5" t="n">
+        <v>0.9978399999999999</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="5" t="n">
         <v>0.99659</v>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>-0.345%</t>
         </is>
       </c>
+      <c r="D45" s="5" t="n">
+        <v>0.99659</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>-0.345%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="5" t="n">
         <v>0.9956700000000001</v>
       </c>
-      <c r="C46" s="0" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>-0.437%</t>
         </is>
       </c>
+      <c r="D46" s="5" t="n">
+        <v>0.9956700000000001</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>-0.437%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="5" t="n">
         <v>0.99419</v>
       </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>-0.585%</t>
         </is>
       </c>
+      <c r="D47" s="5" t="n">
+        <v>0.99419</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>-0.585%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="5" t="n">
         <v>0.99431</v>
       </c>
-      <c r="C48" s="0" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>-0.573%</t>
         </is>
       </c>
+      <c r="D48" s="5" t="n">
+        <v>0.99431</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>-0.573%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="5" t="n">
         <v>0.99477</v>
       </c>
-      <c r="C49" s="0" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>-0.527%</t>
         </is>
       </c>
+      <c r="D49" s="5" t="n">
+        <v>0.99477</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>-0.527%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="5" t="n">
         <v>0.99587</v>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D50" s="5" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="5" t="n">
         <v>0.99679</v>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>-0.325%</t>
         </is>
       </c>
+      <c r="D51" s="5" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="5" t="n">
         <v>0.99732</v>
       </c>
-      <c r="C52" s="0" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>-0.272%</t>
         </is>
       </c>
+      <c r="D52" s="5" t="n">
+        <v>0.99732</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>-0.272%</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="5" t="n">
         <v>0.99678</v>
       </c>
-      <c r="C53" s="0" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>-0.326%</t>
         </is>
       </c>
+      <c r="D53" s="5" t="n">
+        <v>0.99678</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>-0.326%</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="5" t="n">
         <v>0.99704</v>
       </c>
-      <c r="C54" s="0" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
+      <c r="D54" s="5" t="n">
+        <v>0.99704</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="5" t="n">
         <v>0.99718</v>
       </c>
-      <c r="C55" s="0" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>-0.286%</t>
         </is>
       </c>
+      <c r="D55" s="5" t="n">
+        <v>0.99718</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>-0.286%</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="5" t="n">
         <v>0.99717</v>
       </c>
-      <c r="C56" s="0" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>-0.287%</t>
         </is>
       </c>
+      <c r="D56" s="5" t="n">
+        <v>0.99717</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>-0.287%</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="5" t="n">
         <v>0.99721</v>
       </c>
-      <c r="C57" s="0" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>-0.283%</t>
         </is>
       </c>
+      <c r="D57" s="5" t="n">
+        <v>0.99721</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>-0.283%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="5" t="n">
         <v>0.9973</v>
       </c>
-      <c r="C58" s="0" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>-0.274%</t>
         </is>
       </c>
+      <c r="D58" s="5" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>-0.274%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="5" t="n">
         <v>0.99747</v>
       </c>
-      <c r="C59" s="0" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D59" s="5" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="5" t="n">
         <v>0.99765</v>
       </c>
-      <c r="C60" s="0" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>-0.239%</t>
         </is>
       </c>
+      <c r="D60" s="5" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>-0.239%</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="5" t="n">
         <v>0.99761</v>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D61" s="5" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="5" t="n">
         <v>0.99726</v>
       </c>
-      <c r="C62" s="0" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>-0.278%</t>
         </is>
       </c>
+      <c r="D62" s="5" t="n">
+        <v>0.99726</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>-0.278%</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="5" t="n">
         <v>0.99598</v>
       </c>
-      <c r="C63" s="0" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>-0.406%</t>
         </is>
       </c>
+      <c r="D63" s="5" t="n">
+        <v>0.99598</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>-0.406%</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="5" t="n">
         <v>0.9962</v>
       </c>
-      <c r="C64" s="0" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>-0.384%</t>
         </is>
       </c>
+      <c r="D64" s="5" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>-0.384%</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="5" t="n">
         <v>0.99654</v>
       </c>
-      <c r="C65" s="0" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
+      <c r="D65" s="5" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="5" t="n">
         <v>0.99668</v>
       </c>
-      <c r="C66" s="0" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>-0.336%</t>
         </is>
       </c>
+      <c r="D66" s="5" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>-0.336%</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-0.6955%</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-0.343%</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-0.3434%</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2632,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="7" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="8" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2090,32 +2646,50 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="20" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -2125,12 +2699,20 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -2143,9 +2725,17 @@
           <t>-0.002%</t>
         </is>
       </c>
+      <c r="D4" s="0" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -2155,12 +2745,20 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -2170,12 +2768,20 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1.00004</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -2188,9 +2794,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -2203,9 +2817,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -2218,9 +2840,17 @@
           <t>-0.048%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99956</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.048%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -2233,9 +2863,17 @@
           <t>-0.018%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99986</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.018%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -2248,9 +2886,17 @@
           <t>-0.046%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99958</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.046%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -2263,9 +2909,17 @@
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -2278,9 +2932,17 @@
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99984</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -2293,9 +2955,17 @@
           <t>-0.064%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.064%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -2308,9 +2978,17 @@
           <t>-0.066%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.066%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -2323,9 +3001,17 @@
           <t>-0.099%</t>
         </is>
       </c>
+      <c r="D16" s="0" t="n">
+        <v>0.99905</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>-0.099%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -2338,9 +3024,17 @@
           <t>-0.233%</t>
         </is>
       </c>
+      <c r="D17" s="0" t="n">
+        <v>0.99771</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>-0.233%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -2353,9 +3047,17 @@
           <t>-0.229%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>0.99775</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.229%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -2368,9 +3070,17 @@
           <t>-0.228%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>0.99776</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.228%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -2383,9 +3093,17 @@
           <t>-0.224%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.224%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -2398,9 +3116,17 @@
           <t>-0.216%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>0.99788</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.216%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -2413,9 +3139,17 @@
           <t>-0.206%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99798</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.206%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -2428,9 +3162,17 @@
           <t>-0.198%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9980599999999999</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.198%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -2443,9 +3185,17 @@
           <t>-0.205%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.205%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -2458,9 +3208,17 @@
           <t>-0.194%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.194%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -2473,9 +3231,17 @@
           <t>-0.191%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>0.99813</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.191%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -2488,9 +3254,17 @@
           <t>-0.179%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0.99825</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.179%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -2503,9 +3277,17 @@
           <t>-0.175%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>0.99829</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.175%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -2518,9 +3300,17 @@
           <t>-0.131%</t>
         </is>
       </c>
+      <c r="D29" s="0" t="n">
+        <v>0.99873</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>-0.131%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -2533,9 +3323,17 @@
           <t>-0.126%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.126%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -2548,9 +3346,17 @@
           <t>-0.091%</t>
         </is>
       </c>
+      <c r="D31" s="0" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>-0.091%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -2563,9 +3369,17 @@
           <t>-0.481%</t>
         </is>
       </c>
+      <c r="D32" s="0" t="n">
+        <v>0.9952299999999999</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>-0.481%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -2578,9 +3392,17 @@
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D33" s="0" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -2593,9 +3415,17 @@
           <t>-0.391%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>0.99613</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.391%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -2608,9 +3438,17 @@
           <t>-0.387%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>0.99617</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.387%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -2623,9 +3461,17 @@
           <t>-0.354%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.354%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -2638,9 +3484,17 @@
           <t>-0.107%</t>
         </is>
       </c>
+      <c r="D37" s="0" t="n">
+        <v>0.99897</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>-0.107%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -2653,9 +3507,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D38" s="0" t="n">
+        <v>0.99899</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -2668,9 +3530,17 @@
           <t>-0.096%</t>
         </is>
       </c>
+      <c r="D39" s="0" t="n">
+        <v>0.99908</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>-0.096%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -2683,9 +3553,17 @@
           <t>-0.159%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>0.9984499999999999</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.159%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -2698,9 +3576,17 @@
           <t>-0.262%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>0.99742</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.262%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -2713,9 +3599,17 @@
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -2728,9 +3622,17 @@
           <t>-0.238%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>0.99766</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.238%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -2743,9 +3645,17 @@
           <t>-0.201%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>0.99803</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.201%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -2758,9 +3668,17 @@
           <t>-0.324%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.324%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -2773,9 +3691,17 @@
           <t>-0.419%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>0.99585</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-0.419%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -2788,9 +3714,17 @@
           <t>-0.566%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>0.99438</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-0.566%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -2803,9 +3737,17 @@
           <t>-0.553%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>0.99451</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-0.553%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -2818,9 +3760,17 @@
           <t>-0.527%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>0.99477</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-0.527%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -2833,9 +3783,17 @@
           <t>-0.417%</t>
         </is>
       </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99587</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-0.417%</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -2848,9 +3806,17 @@
           <t>-0.325%</t>
         </is>
       </c>
+      <c r="D51" s="0" t="n">
+        <v>0.99679</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>-0.325%</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -2863,9 +3829,17 @@
           <t>-0.272%</t>
         </is>
       </c>
+      <c r="D52" s="0" t="n">
+        <v>0.99732</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>-0.272%</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -2878,9 +3852,17 @@
           <t>-0.326%</t>
         </is>
       </c>
+      <c r="D53" s="0" t="n">
+        <v>0.99678</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>-0.326%</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -2893,9 +3875,17 @@
           <t>-0.3%</t>
         </is>
       </c>
+      <c r="D54" s="0" t="n">
+        <v>0.99704</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -2908,9 +3898,17 @@
           <t>-0.286%</t>
         </is>
       </c>
+      <c r="D55" s="0" t="n">
+        <v>0.99718</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>-0.286%</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -2923,9 +3921,17 @@
           <t>-0.287%</t>
         </is>
       </c>
+      <c r="D56" s="0" t="n">
+        <v>0.99717</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>-0.287%</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -2938,9 +3944,17 @@
           <t>-0.283%</t>
         </is>
       </c>
+      <c r="D57" s="0" t="n">
+        <v>0.99721</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>-0.283%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -2953,9 +3967,17 @@
           <t>-0.274%</t>
         </is>
       </c>
+      <c r="D58" s="0" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>-0.274%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -2968,9 +3990,17 @@
           <t>-0.257%</t>
         </is>
       </c>
+      <c r="D59" s="0" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>-0.257%</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -2983,9 +4013,17 @@
           <t>-0.239%</t>
         </is>
       </c>
+      <c r="D60" s="0" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>-0.239%</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -2998,9 +4036,17 @@
           <t>-0.243%</t>
         </is>
       </c>
+      <c r="D61" s="0" t="n">
+        <v>0.99761</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>-0.243%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -3013,9 +4059,17 @@
           <t>-0.278%</t>
         </is>
       </c>
+      <c r="D62" s="0" t="n">
+        <v>0.99726</v>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>-0.278%</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -3028,9 +4082,17 @@
           <t>-0.406%</t>
         </is>
       </c>
+      <c r="D63" s="0" t="n">
+        <v>0.99598</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>-0.406%</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -3043,9 +4105,17 @@
           <t>-0.384%</t>
         </is>
       </c>
+      <c r="D64" s="0" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>-0.384%</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -3058,9 +4128,17 @@
           <t>-0.35%</t>
         </is>
       </c>
+      <c r="D65" s="0" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -3073,9 +4151,17 @@
           <t>-0.336%</t>
         </is>
       </c>
+      <c r="D66" s="0" t="n">
+        <v>0.99668</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>-0.336%</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -3088,19 +4174,12 @@
           <t>-0.343%</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-0.257%</t>
+      <c r="D67" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>-0.343%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +4195,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="7" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="8" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3130,49 +4209,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3182,12 +4287,20 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3197,12 +4310,20 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -3215,9 +4336,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -3230,9 +4359,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -3245,9 +4382,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -3260,9 +4405,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -3275,9 +4428,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -3290,9 +4451,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -3305,9 +4474,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -3320,9 +4497,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -3335,9 +4520,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -3350,9 +4543,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -3362,12 +4563,20 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -3377,12 +4586,20 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00384</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -3395,9 +4612,17 @@
           <t>-0.0976%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.0976%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -3410,9 +4635,17 @@
           <t>-0.0249%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.0249%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -3425,9 +4658,17 @@
           <t>-0.0508%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00333</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0508%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -3440,9 +4681,17 @@
           <t>-0.251%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00132</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.251%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -3455,9 +4704,17 @@
           <t>-0.4074%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99975</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4074%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -3470,9 +4727,17 @@
           <t>-0.4602%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.99922</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4602%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -3485,9 +4750,17 @@
           <t>-0.3267%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00056</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3267%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -3500,9 +4773,17 @@
           <t>-0.3228%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.3228%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -3515,9 +4796,17 @@
           <t>-0.2869%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.00096</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2869%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -3530,9 +4819,17 @@
           <t>-0.4025%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4025%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -3545,9 +4842,17 @@
           <t>-0.1833%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.1833%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -3557,12 +4862,20 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00457</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -3572,12 +4885,20 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00494</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -3587,12 +4908,20 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00596</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -3602,12 +4931,20 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -3617,12 +4954,20 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00916</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -3635,9 +4980,17 @@
           <t>-0.0466%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0466%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -3650,9 +5003,17 @@
           <t>-0.1407%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00774</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.1407%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -3665,9 +5026,17 @@
           <t>-0.1516%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00763</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1516%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -3677,12 +5046,20 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -3692,12 +5069,20 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -3707,12 +5092,20 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -3725,9 +5118,17 @@
           <t>-0.0547%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02353</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0547%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -3740,9 +5141,17 @@
           <t>-0.5273%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01869</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.5273%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -3755,9 +5164,17 @@
           <t>-0.7656%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.7656%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -3770,9 +5187,17 @@
           <t>-0.6972%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01695</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.6972%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -3785,9 +5210,17 @@
           <t>-0.4961%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.4961%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -3800,9 +5233,17 @@
           <t>-0.914%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01473</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.914%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -3815,9 +5256,17 @@
           <t>-1.412%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.412%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -3830,9 +5279,17 @@
           <t>-1.5311%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.00841</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.5311%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -3845,9 +5302,17 @@
           <t>-1.7655%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-1.7655%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -3860,9 +5325,17 @@
           <t>-1.744%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-1.744%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -3875,17 +5348,10 @@
           <t>-1.4257%</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+      <c r="D50" s="0" t="n">
         <v>1.00949</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>-1.4257%</t>
         </is>
@@ -3902,12 +5368,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="7" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="8" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3916,49 +5382,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3968,12 +5460,20 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3983,12 +5483,20 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -4001,9 +5509,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -4016,9 +5532,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -4031,9 +5555,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -4046,9 +5578,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -4061,9 +5601,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -4076,9 +5624,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -4091,9 +5647,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -4106,9 +5670,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -4121,9 +5693,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -4136,9 +5716,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -4148,12 +5736,20 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -4163,12 +5759,20 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -4178,12 +5782,20 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -4193,12 +5805,20 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -4211,9 +5831,17 @@
           <t>-0.0946%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00325</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0946%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -4226,9 +5854,17 @@
           <t>-0.3734%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.3734%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -4241,9 +5877,17 @@
           <t>-0.4551%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99963</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4551%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -4256,9 +5900,17 @@
           <t>-0.4242%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4242%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -4271,9 +5923,17 @@
           <t>-0.3455%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00073</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3455%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -4286,9 +5946,17 @@
           <t>-0.2729%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2729%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -4301,9 +5969,17 @@
           <t>-0.1892%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.1892%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -4316,9 +5992,17 @@
           <t>-0.2599%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2599%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -4331,9 +6015,17 @@
           <t>-0.0239%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0239%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -4343,12 +6035,20 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -4361,9 +6061,17 @@
           <t>-0.0427%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0427%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -4373,12 +6081,20 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00707</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -4388,12 +6104,20 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -4403,12 +6127,20 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00923</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -4421,9 +6153,17 @@
           <t>-0.1199%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.1199%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -4436,9 +6176,17 @@
           <t>-0.2338%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00687</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2338%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -4451,9 +6199,17 @@
           <t>-0.1367%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1367%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -4463,12 +6219,20 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -4478,12 +6242,20 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01723</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -4493,12 +6265,20 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -4511,9 +6291,17 @@
           <t>-0.5679%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02249</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.5679%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -4526,9 +6314,17 @@
           <t>-1.1455%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01655</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-1.1455%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -4541,9 +6337,17 @@
           <t>-1.1164%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-1.1164%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -4556,9 +6360,17 @@
           <t>-1.2233%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01575</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.2233%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -4571,9 +6383,17 @@
           <t>-0.8733%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01935</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.8733%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -4586,9 +6406,17 @@
           <t>-1.3527%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.3527%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -4601,9 +6429,17 @@
           <t>-2.0081%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-2.0081%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4616,9 +6452,17 @@
           <t>-1.8506%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.8506%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4631,9 +6475,17 @@
           <t>-2.0538%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00721</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-2.0538%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4646,9 +6498,17 @@
           <t>-2.1277%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-2.1277%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -4661,19 +6521,12 @@
           <t>-1.5462%</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-2.4486%</t>
+      <c r="D50" s="0" t="n">
+        <v>1.01243</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-1.5462%</t>
         </is>
       </c>
     </row>
@@ -4689,7 +6542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -4698,49 +6551,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -4750,12 +6629,20 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -4765,12 +6652,20 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -4783,9 +6678,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -4798,9 +6701,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -4813,9 +6724,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -4828,9 +6747,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -4843,9 +6770,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -4858,9 +6793,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -4873,9 +6816,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -4888,9 +6839,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -4903,9 +6862,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -4918,9 +6885,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -4930,12 +6905,20 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -4945,12 +6928,20 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00384</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -4963,9 +6954,17 @@
           <t>-0.0976%</t>
         </is>
       </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00286</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>-0.0976%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -4978,9 +6977,17 @@
           <t>-0.0249%</t>
         </is>
       </c>
+      <c r="D19" s="0" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>-0.0249%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -4993,9 +7000,17 @@
           <t>-0.0508%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00333</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0508%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -5008,9 +7023,17 @@
           <t>-0.251%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00132</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.251%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -5023,9 +7046,17 @@
           <t>-0.4074%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99975</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4074%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -5038,9 +7069,17 @@
           <t>-0.4602%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.99922</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4602%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -5053,9 +7092,17 @@
           <t>-0.3267%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00056</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3267%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -5068,9 +7115,17 @@
           <t>-0.3228%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.3228%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -5083,9 +7138,17 @@
           <t>-0.2869%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.00096</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2869%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -5098,9 +7161,17 @@
           <t>-0.4025%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4025%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -5113,9 +7184,17 @@
           <t>-0.1833%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.1833%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -5125,12 +7204,20 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00457</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -5140,12 +7227,20 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00494</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -5155,12 +7250,20 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00596</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -5170,12 +7273,20 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -5185,12 +7296,20 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00916</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -5203,9 +7322,17 @@
           <t>-0.0466%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0466%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -5218,9 +7345,17 @@
           <t>-0.1407%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00774</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.1407%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -5233,9 +7368,17 @@
           <t>-0.1516%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00763</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1516%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -5245,12 +7388,20 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -5260,12 +7411,20 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01567</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -5275,12 +7434,20 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02409</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -5293,9 +7460,17 @@
           <t>-0.0547%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02353</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0547%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -5308,9 +7483,17 @@
           <t>-0.5273%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01869</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.5273%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -5323,9 +7506,17 @@
           <t>-0.7656%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.7656%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -5338,9 +7529,17 @@
           <t>-0.6972%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01695</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.6972%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -5353,9 +7552,17 @@
           <t>-0.4961%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01901</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.4961%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -5368,9 +7575,17 @@
           <t>-0.914%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01473</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.914%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -5383,9 +7598,17 @@
           <t>-1.412%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00963</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.412%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -5398,9 +7621,17 @@
           <t>-1.5311%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.00841</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.5311%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -5413,9 +7644,17 @@
           <t>-1.7655%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-1.7655%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -5428,9 +7667,17 @@
           <t>-1.744%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-1.744%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -5443,19 +7690,12 @@
           <t>-1.4257%</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>2.01898</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="D50" s="0" t="n">
+        <v>1.00949</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-1.4257%</t>
         </is>
       </c>
     </row>
@@ -5470,12 +7710,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="7" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="8" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5484,49 +7724,75 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 净值</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>回撤</t>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-有返息</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-有返息</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 净值-无返息</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>回撤-无返息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -5536,12 +7802,20 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -5551,12 +7825,20 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -5569,9 +7851,17 @@
           <t>-0.113%</t>
         </is>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>0.99893</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>-0.113%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -5584,9 +7874,17 @@
           <t>-0.207%</t>
         </is>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>-0.207%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -5599,9 +7897,17 @@
           <t>-0.271%</t>
         </is>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>0.99735</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>-0.271%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -5614,9 +7920,17 @@
           <t>-0.309%</t>
         </is>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>0.99697</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>-0.309%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -5629,9 +7943,17 @@
           <t>-0.457%</t>
         </is>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>-0.457%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -5644,9 +7966,17 @@
           <t>-0.525%</t>
         </is>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>0.99481</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>-0.525%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -5659,9 +7989,17 @@
           <t>-0.502%</t>
         </is>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>0.99504</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>-0.502%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -5674,9 +8012,17 @@
           <t>-0.463%</t>
         </is>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>0.99543</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>-0.463%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -5689,9 +8035,17 @@
           <t>-0.781%</t>
         </is>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>0.99225</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>-0.781%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -5704,9 +8058,17 @@
           <t>-0.105%</t>
         </is>
       </c>
+      <c r="D15" s="0" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>-0.105%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -5716,12 +8078,20 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -5731,12 +8101,20 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -5746,12 +8124,20 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -5761,12 +8147,20 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1.0042</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -5779,9 +8173,17 @@
           <t>-0.0946%</t>
         </is>
       </c>
+      <c r="D20" s="0" t="n">
+        <v>1.00325</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>-0.0946%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -5794,9 +8196,17 @@
           <t>-0.3734%</t>
         </is>
       </c>
+      <c r="D21" s="0" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>-0.3734%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -5809,9 +8219,17 @@
           <t>-0.4551%</t>
         </is>
       </c>
+      <c r="D22" s="0" t="n">
+        <v>0.99963</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>-0.4551%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -5824,9 +8242,17 @@
           <t>-0.4242%</t>
         </is>
       </c>
+      <c r="D23" s="0" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.4242%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -5839,9 +8265,17 @@
           <t>-0.3455%</t>
         </is>
       </c>
+      <c r="D24" s="0" t="n">
+        <v>1.00073</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.3455%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -5854,9 +8288,17 @@
           <t>-0.2729%</t>
         </is>
       </c>
+      <c r="D25" s="0" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2729%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -5869,9 +8311,17 @@
           <t>-0.1892%</t>
         </is>
       </c>
+      <c r="D26" s="0" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.1892%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -5884,9 +8334,17 @@
           <t>-0.2599%</t>
         </is>
       </c>
+      <c r="D27" s="0" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2599%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -5899,9 +8357,17 @@
           <t>-0.0239%</t>
         </is>
       </c>
+      <c r="D28" s="0" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0239%</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -5911,12 +8377,20 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -5929,9 +8403,17 @@
           <t>-0.0427%</t>
         </is>
       </c>
+      <c r="D30" s="0" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0427%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -5941,12 +8423,20 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1.00707</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -5956,12 +8446,20 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1.00825</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -5971,12 +8469,20 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1.00923</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -5989,9 +8495,17 @@
           <t>-0.1199%</t>
         </is>
       </c>
+      <c r="D34" s="0" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.1199%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -6004,9 +8518,17 @@
           <t>-0.2338%</t>
         </is>
       </c>
+      <c r="D35" s="0" t="n">
+        <v>1.00687</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2338%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -6019,9 +8541,17 @@
           <t>-0.1367%</t>
         </is>
       </c>
+      <c r="D36" s="0" t="n">
+        <v>1.00785</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.1367%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -6031,12 +8561,20 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -6046,12 +8584,20 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1.01723</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -6061,12 +8607,20 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -6079,9 +8633,17 @@
           <t>-0.5679%</t>
         </is>
       </c>
+      <c r="D40" s="0" t="n">
+        <v>1.02249</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.5679%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -6094,9 +8656,17 @@
           <t>-1.1455%</t>
         </is>
       </c>
+      <c r="D41" s="0" t="n">
+        <v>1.01655</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-1.1455%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -6109,9 +8679,17 @@
           <t>-1.1164%</t>
         </is>
       </c>
+      <c r="D42" s="0" t="n">
+        <v>1.01685</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-1.1164%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -6124,9 +8702,17 @@
           <t>-1.2233%</t>
         </is>
       </c>
+      <c r="D43" s="0" t="n">
+        <v>1.01575</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.2233%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -6139,9 +8725,17 @@
           <t>-0.8733%</t>
         </is>
       </c>
+      <c r="D44" s="0" t="n">
+        <v>1.01935</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.8733%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -6154,9 +8748,17 @@
           <t>-1.3527%</t>
         </is>
       </c>
+      <c r="D45" s="0" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.3527%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -6169,9 +8771,17 @@
           <t>-2.0081%</t>
         </is>
       </c>
+      <c r="D46" s="0" t="n">
+        <v>1.00768</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-2.0081%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -6184,9 +8794,17 @@
           <t>-1.8506%</t>
         </is>
       </c>
+      <c r="D47" s="0" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-1.8506%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -6199,9 +8817,17 @@
           <t>-2.0538%</t>
         </is>
       </c>
+      <c r="D48" s="0" t="n">
+        <v>1.00721</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-2.0538%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -6214,9 +8840,17 @@
           <t>-2.1277%</t>
         </is>
       </c>
+      <c r="D49" s="0" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-2.1277%</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -6229,19 +8863,12 @@
           <t>-1.5462%</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>2.0063</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="D50" s="0" t="n">
+        <v>1.01243</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-1.5462%</t>
         </is>
       </c>
     </row>

--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="22095" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="22095" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -631,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -677,7 +677,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -688,6 +690,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1066,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2603,18 +2606,41 @@
           <t>2025/05/29</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="5" t="n">
         <v>0.99308</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>-0.3434%</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
         <is>
           <t>-0.6955%</t>
         </is>
       </c>
-      <c r="D67" t="n">
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.99308</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-0.6955%</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>0.99661</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>-0.3434%</t>
         </is>
@@ -2632,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -2676,7 +2702,7 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D2" s="18" t="n">
@@ -2684,7 +2710,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2725,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D3" s="0" t="n">
@@ -2707,7 +2733,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2771,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D5" s="0" t="n">
@@ -2753,7 +2779,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2794,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D6" s="0" t="n">
@@ -2776,7 +2802,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4161,25 +4187,48 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="21" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
       </c>
       <c r="B67" s="0" t="n">
-        <v>0.99661</v>
+        <v>0.99444</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>-0.343%</t>
+          <t>-0.2568%</t>
         </is>
       </c>
       <c r="D67" s="0" t="n">
-        <v>0.99661</v>
+        <v>0.99747</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>-0.343%</t>
+          <t>-0.5599%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.99444</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-0.5599%</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.99747</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-0.2568%</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4280,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -4254,7 +4303,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -5335,27 +5384,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="n">
-        <v>1.00949</v>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>-1.4257%</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>1.00949</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>-1.4257%</t>
-        </is>
-      </c>
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="0" t="n"/>
+      <c r="C50" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5404,7 +5435,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -5427,7 +5458,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -6508,27 +6539,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="n">
-        <v>1.01243</v>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>-1.5462%</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>1.01243</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>-1.5462%</t>
-        </is>
-      </c>
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="0" t="n"/>
+      <c r="C50" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6573,7 +6586,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -6596,7 +6609,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -7677,27 +7690,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="n">
-        <v>1.00949</v>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>-1.4257%</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>1.00949</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>-1.4257%</t>
-        </is>
-      </c>
+      <c r="A50" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7746,7 +7739,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -7769,7 +7762,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -8850,27 +8843,9 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="n">
-        <v>1.01243</v>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>-1.5462%</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>1.01243</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>-1.5462%</t>
-        </is>
-      </c>
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="0" t="n"/>
+      <c r="C50" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/template/5.29/净值.xlsx
+++ b/template/5.29/净值.xlsx
@@ -20,13 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.00000_ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="168" formatCode="yyyy\/mm\/dd"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -631,7 +630,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -677,9 +676,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -690,7 +686,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1069,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="9" min="1" max="1"/>
@@ -2601,50 +2596,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>-0.3434%</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>-0.6955%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.99308</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-0.6955%</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0.99661</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-0.3434%</t>
-        </is>
-      </c>
+      <c r="A67" s="16" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="0" t="n"/>
+      <c r="E67" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2658,12 +2614,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2694,28 +2650,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="19" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -2738,7 +2694,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -2761,7 +2717,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -2784,7 +2740,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -2807,7 +2763,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -2830,7 +2786,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -2853,7 +2809,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -2876,7 +2832,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -2899,7 +2855,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -2922,7 +2878,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -2945,7 +2901,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -2968,7 +2924,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -2991,7 +2947,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -3014,7 +2970,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -3037,7 +2993,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -3060,7 +3016,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -3083,7 +3039,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -3106,7 +3062,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -3129,7 +3085,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3152,7 +3108,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3175,7 +3131,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -3198,7 +3154,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -3221,7 +3177,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -3244,7 +3200,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -3267,7 +3223,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -3290,7 +3246,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -3313,7 +3269,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -3336,7 +3292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -3359,7 +3315,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -3382,7 +3338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -3405,7 +3361,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -3428,7 +3384,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -3451,7 +3407,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -3474,7 +3430,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -3497,7 +3453,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -3520,7 +3476,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -3543,7 +3499,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -3566,7 +3522,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -3589,7 +3545,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -3612,7 +3568,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -3635,7 +3591,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -3658,7 +3614,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -3681,7 +3637,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -3704,7 +3660,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -3727,7 +3683,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -3750,7 +3706,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -3773,7 +3729,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -3796,7 +3752,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -3819,7 +3775,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -3842,7 +3798,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -3865,7 +3821,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -3888,7 +3844,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -3911,7 +3867,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -3934,7 +3890,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -3957,7 +3913,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -3980,7 +3936,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -4003,7 +3959,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -4026,7 +3982,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -4049,7 +4005,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="21" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -4072,7 +4028,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="21" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -4095,7 +4051,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="A63" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -4118,7 +4074,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="21" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4141,7 +4097,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4164,7 +4120,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4187,50 +4143,9 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B67" s="0" t="n">
-        <v>0.99444</v>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>-0.2568%</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>-0.5599%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.99444</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>-0.5599%</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0.99747</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-0.2568%</t>
-        </is>
-      </c>
+      <c r="A67" s="20" t="n"/>
+      <c r="B67" s="0" t="n"/>
+      <c r="C67" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4248,8 +4163,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4280,53 +4195,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -4349,7 +4264,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -4372,7 +4287,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -4395,7 +4310,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -4418,7 +4333,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -4441,7 +4356,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -4464,7 +4379,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -4487,7 +4402,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -4510,7 +4425,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -4533,7 +4448,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -4556,7 +4471,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -4579,7 +4494,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -4602,7 +4517,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -4625,7 +4540,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -4648,7 +4563,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -4671,7 +4586,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -4694,7 +4609,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -4717,7 +4632,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -4740,7 +4655,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -4763,7 +4678,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -4786,7 +4701,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -4809,7 +4724,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -4832,7 +4747,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -4855,7 +4770,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -4878,7 +4793,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -4901,7 +4816,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -4924,7 +4839,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -4947,7 +4862,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -4970,7 +4885,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -4993,7 +4908,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -5016,7 +4931,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -5039,7 +4954,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -5062,7 +4977,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -5085,7 +5000,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -5108,7 +5023,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -5131,7 +5046,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -5154,7 +5069,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -5177,7 +5092,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -5200,7 +5115,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -5223,7 +5138,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -5246,7 +5161,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -5269,7 +5184,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -5292,7 +5207,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -5315,7 +5230,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -5338,7 +5253,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -5361,7 +5276,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -5384,7 +5299,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="20" t="n"/>
       <c r="B50" s="0" t="n"/>
       <c r="C50" s="0" t="n"/>
     </row>
@@ -5403,8 +5318,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5435,53 +5350,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -5504,7 +5419,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -5527,7 +5442,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -5550,7 +5465,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -5573,7 +5488,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -5596,7 +5511,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -5619,7 +5534,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -5642,7 +5557,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -5665,7 +5580,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -5688,7 +5603,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -5711,7 +5626,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -5734,7 +5649,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -5757,7 +5672,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -5780,7 +5695,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -5803,7 +5718,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -5826,7 +5741,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -5849,7 +5764,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -5872,7 +5787,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -5895,7 +5810,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -5918,7 +5833,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -5941,7 +5856,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -5964,7 +5879,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -5987,7 +5902,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -6010,7 +5925,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -6033,7 +5948,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -6056,7 +5971,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -6079,7 +5994,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -6102,7 +6017,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -6125,7 +6040,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -6148,7 +6063,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -6171,7 +6086,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -6194,7 +6109,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -6217,7 +6132,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -6240,7 +6155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -6263,7 +6178,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -6286,7 +6201,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -6309,7 +6224,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -6332,7 +6247,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -6355,7 +6270,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -6378,7 +6293,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -6401,7 +6316,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -6424,7 +6339,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -6447,7 +6362,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -6470,7 +6385,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -6493,7 +6408,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -6516,7 +6431,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -6539,7 +6454,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="20" t="n"/>
       <c r="B50" s="0" t="n"/>
       <c r="C50" s="0" t="n"/>
     </row>
@@ -6586,53 +6501,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="n">
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -6642,7 +6557,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D4" s="0" t="n">
@@ -6650,12 +6565,12 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -6665,7 +6580,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D5" s="0" t="n">
@@ -6673,12 +6588,12 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -6701,7 +6616,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -6724,7 +6639,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -6747,7 +6662,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -6770,7 +6685,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -6793,7 +6708,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -6816,7 +6731,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -6839,7 +6754,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -6862,7 +6777,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -6885,7 +6800,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -6908,7 +6823,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -6918,7 +6833,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -6926,12 +6841,12 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -6941,7 +6856,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -6949,12 +6864,12 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -6977,7 +6892,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -7000,7 +6915,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -7023,7 +6938,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -7046,7 +6961,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -7069,7 +6984,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -7092,7 +7007,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -7115,7 +7030,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -7138,7 +7053,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -7161,7 +7076,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -7184,7 +7099,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -7207,7 +7122,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -7217,7 +7132,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D29" s="0" t="n">
@@ -7225,12 +7140,12 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -7240,7 +7155,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D30" s="0" t="n">
@@ -7248,12 +7163,12 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -7263,7 +7178,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D31" s="0" t="n">
@@ -7271,12 +7186,12 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -7286,7 +7201,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D32" s="0" t="n">
@@ -7294,12 +7209,12 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -7309,7 +7224,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D33" s="0" t="n">
@@ -7317,12 +7232,12 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -7345,7 +7260,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -7368,7 +7283,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -7391,7 +7306,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -7401,7 +7316,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D37" s="0" t="n">
@@ -7409,12 +7324,12 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -7424,7 +7339,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D38" s="0" t="n">
@@ -7432,12 +7347,12 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -7447,7 +7362,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D39" s="0" t="n">
@@ -7455,12 +7370,12 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -7483,7 +7398,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -7506,7 +7421,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -7529,7 +7444,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -7552,7 +7467,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -7575,7 +7490,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -7598,7 +7513,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -7621,7 +7536,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -7644,7 +7559,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -7667,7 +7582,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -7690,7 +7605,23 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="20" t="n"/>
+      <c r="B50" s="0" t="n">
+        <v>2.01898</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>2.01698</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7707,8 +7638,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="18" min="2" max="2"/>
-    <col width="10.775" customWidth="1" style="19" min="3" max="3"/>
+    <col width="9.66666666666667" customWidth="1" style="17" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7739,53 +7670,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="n">
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -7795,7 +7726,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D4" s="0" t="n">
@@ -7803,12 +7734,12 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -7818,7 +7749,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D5" s="0" t="n">
@@ -7826,12 +7757,12 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -7854,7 +7785,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -7877,7 +7808,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -7900,7 +7831,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -7923,7 +7854,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -7946,7 +7877,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -7969,7 +7900,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -7992,7 +7923,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -8015,7 +7946,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -8038,7 +7969,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -8061,7 +7992,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -8071,7 +8002,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D16" s="0" t="n">
@@ -8079,12 +8010,12 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -8094,7 +8025,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D17" s="0" t="n">
@@ -8102,12 +8033,12 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -8117,7 +8048,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D18" s="0" t="n">
@@ -8125,12 +8056,12 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -8140,7 +8071,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D19" s="0" t="n">
@@ -8148,12 +8079,12 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -8176,7 +8107,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -8199,7 +8130,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -8222,7 +8153,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -8245,7 +8176,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -8268,7 +8199,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -8291,7 +8222,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -8314,7 +8245,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -8337,7 +8268,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -8360,7 +8291,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -8370,7 +8301,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D29" s="0" t="n">
@@ -8378,12 +8309,12 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -8406,7 +8337,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -8416,7 +8347,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D31" s="0" t="n">
@@ -8424,12 +8355,12 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -8439,7 +8370,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D32" s="0" t="n">
@@ -8447,12 +8378,12 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -8462,7 +8393,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D33" s="0" t="n">
@@ -8470,12 +8401,12 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -8498,7 +8429,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -8521,7 +8452,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -8544,7 +8475,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -8554,7 +8485,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D37" s="0" t="n">
@@ -8562,12 +8493,12 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -8577,7 +8508,7 @@
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D38" s="0" t="n">
@@ -8585,12 +8516,12 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -8600,7 +8531,7 @@
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D39" s="0" t="n">
@@ -8608,12 +8539,12 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -8636,7 +8567,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -8659,7 +8590,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -8682,7 +8613,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -8705,7 +8636,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -8728,7 +8659,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -8751,7 +8682,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -8774,7 +8705,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -8797,7 +8728,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -8820,7 +8751,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -8843,9 +8774,23 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
-      <c r="B50" s="0" t="n"/>
-      <c r="C50" s="0" t="n"/>
+      <c r="A50" s="20" t="n"/>
+      <c r="B50" s="0" t="n">
+        <v>2.0063</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>2.0043</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
